--- a/PVI-TMDT-Data.xlsx
+++ b/PVI-TMDT-Data.xlsx
@@ -11,9 +11,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TONG HOP" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DU AN" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBOOKING" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DIEM NONG" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KHO KHAN - HO TRO" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOC THOI GIAN" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PHAN CONG" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GANTT" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -602,7 +603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C21"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -610,6 +611,7 @@
     <col width="95" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -624,6 +626,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -639,7 +642,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Hàng tháng, điền số mới vào các ô CHỮ XANH DƯƠNG ở các sheet: DU AN, WBOOKING, DIEM NONG, MOC THOI GIAN, PHAN CONG.</t>
+          <t>Hàng tháng, điền số mới vào các ô CHỮ XANH DƯƠNG ở các sheet: DU AN, WBOOKING, KHO KHAN - HO TRO, GANTT, MOC THOI GIAN, PHAN CONG.</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2111,7 +2114,7 @@
     <row r="1">
       <c r="A1" s="17" t="inlineStr">
         <is>
-          <t>ĐIỂM NÓNG CẦN LÃNH ĐẠO QUYẾT ĐỊNH — Khối C dashboard · Mức độ: GAP hoặc THEO-DOI</t>
+          <t>DỰ ÁN GẶP KHÓ KHĂN / CẦN LÃNH ĐẠO HỖ TRỢ — Khối C dashboard · Mức độ: GAP hoặc THEO-DOI</t>
         </is>
       </c>
     </row>
@@ -2128,12 +2131,12 @@
       </c>
       <c r="C2" s="18" t="inlineStr">
         <is>
-          <t>Vấn đề</t>
+          <t>Khó khăn</t>
         </is>
       </c>
       <c r="D2" s="18" t="inlineStr">
         <is>
-          <t>Đề xuất trình lãnh đạo</t>
+          <t>Cần lãnh đạo hỗ trợ</t>
         </is>
       </c>
     </row>
@@ -2150,12 +2153,12 @@
       </c>
       <c r="C3" s="25" t="inlineStr">
         <is>
-          <t>Tờ trình tăng ĐMCP bị Ban KTKH từ chối</t>
+          <t>Tờ trình tăng ĐMCP bị Ban KTKH từ chối; ~64% user từ chối tái tục sau khi hết KM miễn phí</t>
         </is>
       </c>
       <c r="D3" s="25" t="inlineStr">
         <is>
-          <t>Chốt hướng: PVI chịu chi phí KM tháng đầu / phương án nâng giá 40% của ZLP</t>
+          <t>Chốt hướng triển khai mới: PVI chịu chi phí KM tháng đầu / phương án ZLP (nâng giá 40%, giảm 50% cho user, commission 60%)</t>
         </is>
       </c>
     </row>
@@ -2172,12 +2175,12 @@
       </c>
       <c r="C4" s="25" t="inlineStr">
         <is>
-          <t>Công nợ BAV quá hạn 277.972.704đ (T3–5/2026)</t>
+          <t>Công nợ BAV quá hạn 277.972.704đ (T3–5/2026) — đã gửi mail &amp; công văn nhưng chưa thu được</t>
         </is>
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t>Chỉ đạo phương án thu hồi công nợ</t>
+          <t>Chỉ đạo phương án thu hồi công nợ; tác động BAV ở cấp lãnh đạo</t>
         </is>
       </c>
     </row>
@@ -2189,17 +2192,17 @@
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>Asahi NPUV + APUV</t>
+          <t>Asahi (NPUV + APUV)</t>
         </is>
       </c>
       <c r="C5" s="25" t="inlineStr">
         <is>
-          <t>Cả hai giảm &gt;26% so cùng kỳ</t>
+          <t>Cả hai sản phẩm giảm &gt;26% so cùng kỳ; NPUV2/APUV2 vẫn chờ Asahi phản hồi</t>
         </is>
       </c>
       <c r="D5" s="25" t="inlineStr">
         <is>
-          <t>Duyệt phương án lấy lead bệnh viện + điều chỉnh APUV</t>
+          <t>Duyệt phương án lấy lead tại bệnh viện + chủ trương điều chỉnh sản phẩm APUV</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2219,12 @@
       </c>
       <c r="C6" s="25" t="inlineStr">
         <is>
-          <t>Tỷ lệ bồi thường 87,66% (T4–T6 đều &gt;100%)</t>
+          <t>Tỷ lệ bồi thường 87,66%; T4–T6 đều vượt 100% — rủi ro lỗ nghiệp vụ</t>
         </is>
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t>Rà soát gói B20, cơ cấu tái — rủi ro lỗ</t>
+          <t>Cho ý kiến rà soát gói B20 và cơ cấu tái</t>
         </is>
       </c>
     </row>
@@ -2233,17 +2236,39 @@
       </c>
       <c r="B7" s="25" t="inlineStr">
         <is>
+          <t>SPA GoSafe</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>Chubb chậm thống nhất HĐ 3 bên &amp; biểu phí — rủi ro lùi mốc go-live 06/08</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>Tác động Chubb ở cấp cao để chốt hợp đồng trong tuần đầu T7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>THEO-DOI</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
           <t>MobiFone</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
-        <is>
-          <t>Mới đạt 1,05% KPI</t>
-        </is>
-      </c>
-      <c r="D7" s="25" t="inlineStr">
-        <is>
-          <t>Đẩy ký MOU + go-live Cổng BH</t>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>Mới đạt 1,05% KPI năm; MOU hợp tác chiến lược chưa ký</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
+        <is>
+          <t>Thu xếp ký MOU cấp lãnh đạo hai bên để mở khóa Cổng BH</t>
         </is>
       </c>
     </row>
@@ -3073,4 +3098,631 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>GANTT KẾ HOẠCH T7–T8 — Khối E dashboard · Từ/Đến dạng dd/mm · Từ = Đến nghĩa là mốc (hình thoi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>Dự án</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="inlineStr">
+        <is>
+          <t>Nội dung</t>
+        </is>
+      </c>
+      <c r="C2" s="18" t="inlineStr">
+        <is>
+          <t>Từ (dd/mm)</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="inlineStr">
+        <is>
+          <t>Đến (dd/mm)</t>
+        </is>
+      </c>
+      <c r="E2" s="18" t="inlineStr">
+        <is>
+          <t>Trạng thái màu</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>TripCARE</t>
+        </is>
+      </c>
+      <c r="B3" s="25" t="inlineStr">
+        <is>
+          <t>Chốt cơ cấu tái với Chubb</t>
+        </is>
+      </c>
+      <c r="C3" s="25" t="inlineStr">
+        <is>
+          <t>01/07</t>
+        </is>
+      </c>
+      <c r="D3" s="25" t="inlineStr">
+        <is>
+          <t>15/07</t>
+        </is>
+      </c>
+      <c r="E3" s="25" t="inlineStr">
+        <is>
+          <t>tang-truong</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>TripCARE</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>Go-live Phase 2 UI/UX (Insider)</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>15/07</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>31/07</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>tang-truong</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>SPA GoSafe</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>Hoàn thiện back-end</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t>01/07</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
+        <is>
+          <t>14/07</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>sap-golive</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>SPA GoSafe</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>UAT với 1A</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="inlineStr">
+        <is>
+          <t>13/07</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
+        <is>
+          <t>24/07</t>
+        </is>
+      </c>
+      <c r="E6" s="25" t="inlineStr">
+        <is>
+          <t>sap-golive</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>SPA GoSafe</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>Production Chubb CRS</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>06/08</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>06/08</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t>sap-golive</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>Viettel Store</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>Đổi nhà tái → AIG</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>01/07</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
+        <is>
+          <t>01/07</t>
+        </is>
+      </c>
+      <c r="E8" s="25" t="inlineStr">
+        <is>
+          <t>sap-golive</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>Viettel Store</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>Go-live ADLD &amp; EW</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="inlineStr">
+        <is>
+          <t>01/07</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>20/07</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t>sap-golive</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>Viettel Store</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>Kết nối '1 đổi 1'</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>31/07</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>sap-golive</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>Sun Group</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>Ký MOU OPES · kết nối · go-live trước 31/07</t>
+        </is>
+      </c>
+      <c r="C11" s="25" t="inlineStr">
+        <is>
+          <t>01/07</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
+          <t>31/07</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>sap-golive</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>Flight Delay</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>Test claim portal Igloo</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="inlineStr">
+        <is>
+          <t>01/07</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>14/07</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
+          <t>sap-golive</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>Flight Delay</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>Triển khai OTA</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="inlineStr">
+        <is>
+          <t>14/07</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>31/07</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>sap-golive</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>MobiFone</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>Bản test Cổng BH</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="inlineStr">
+        <is>
+          <t>02/07</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>02/07</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="inlineStr">
+        <is>
+          <t>cho-doi-tac</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>MobiFone</t>
+        </is>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>Ký MOU · go-live BH DLQT</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
+          <t>05/07</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>25/07</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="inlineStr">
+        <is>
+          <t>cho-doi-tac</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>Asahi</t>
+        </is>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>Review landing page lead bệnh viện</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t>01/07</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
+        <is>
+          <t>canh-bao</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>Asahi</t>
+        </is>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>Triển khai NPUV2 · thưởng TSR</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>31/07</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
+        <is>
+          <t>canh-bao</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>Zalopay</t>
+        </is>
+      </c>
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t>Trình lãnh đạo phương án mới</t>
+        </is>
+      </c>
+      <c r="C18" s="25" t="inlineStr">
+        <is>
+          <t>01/07</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>15/07</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="inlineStr">
+        <is>
+          <t>cho-doi-tac</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>Plus &amp; EW Honda</t>
+        </is>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>Nâng cấp hondaplus.vn GĐ2</t>
+        </is>
+      </c>
+      <c r="C19" s="25" t="inlineStr">
+        <is>
+          <t>01/07</t>
+        </is>
+      </c>
+      <c r="D19" s="25" t="inlineStr">
+        <is>
+          <t>31/07</t>
+        </is>
+      </c>
+      <c r="E19" s="25" t="inlineStr">
+        <is>
+          <t>tang-truong</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>Plus &amp; EW Honda</t>
+        </is>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>Mở rộng HEAD tỉnh</t>
+        </is>
+      </c>
+      <c r="C20" s="25" t="inlineStr">
+        <is>
+          <t>15/07</t>
+        </is>
+      </c>
+      <c r="D20" s="25" t="inlineStr">
+        <is>
+          <t>10/08</t>
+        </is>
+      </c>
+      <c r="E20" s="25" t="inlineStr">
+        <is>
+          <t>tang-truong</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>BambooCARE</t>
+        </is>
+      </c>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>Thu hồi công nợ BAV</t>
+        </is>
+      </c>
+      <c r="C21" s="25" t="inlineStr">
+        <is>
+          <t>01/07</t>
+        </is>
+      </c>
+      <c r="D21" s="25" t="inlineStr">
+        <is>
+          <t>31/07</t>
+        </is>
+      </c>
+      <c r="E21" s="25" t="inlineStr">
+        <is>
+          <t>canh-bao</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>wBooking</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>Đào tạo sân golf Vinpearl</t>
+        </is>
+      </c>
+      <c r="C22" s="25" t="inlineStr">
+        <is>
+          <t>01/07</t>
+        </is>
+      </c>
+      <c r="D22" s="25" t="inlineStr">
+        <is>
+          <t>20/07</t>
+        </is>
+      </c>
+      <c r="E22" s="25" t="inlineStr">
+        <is>
+          <t>canh-bao</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>wBooking</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>Rà soát gói B20</t>
+        </is>
+      </c>
+      <c r="C23" s="25" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="D23" s="25" t="inlineStr">
+        <is>
+          <t>31/07</t>
+        </is>
+      </c>
+      <c r="E23" s="25" t="inlineStr">
+        <is>
+          <t>canh-bao</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="E3:E31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"tang-truong,sap-golive,canh-bao,cho-doi-tac"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>